--- a/Matchbook_Culture_Data.xlsx
+++ b/Matchbook_Culture_Data.xlsx
@@ -1121,7 +1121,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>MET | Skeletons/Morning_Meeting_Observation_Tool.md; 13/Morning_Meeting_Walkthrough_Form.md; 13/Rubric_Alignment_Crosswalk.md</t>
+          <t>MET | Skeletons/Morning_Meeting_Observation_Tool.md; Skeletons/Morning_Meeting_Rubric_Alignment_Crosswalk.md; 13/Morning_Meeting_Walkthrough_Form.md; 13/Rubric_Alignment_Crosswalk.md | Formal ratings use the Matchbook SRR Teacher rubric.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CLOSED | Interactive guide and observation logic have editable markdown counterparts in Skeletons.</t>
+          <t>CLOSED 2026-06-15 | Morning Meeting crosswalk rebuilt against the Matchbook SRR Teacher rubric; Coach edition and Get Better Faster positioned as coaching guidance.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CLOSED 2026-06-04: Morning Meeting logic converted to editable docs through Skeletons program manual, observation tool, data tracker, prompt banks, and grade-band adaptation guide.</t>
+          <t>CLOSED 2026-06-15: Morning Meeting logic has editable masters, and its observation/crosswalk layer now uses the formal Matchbook SRR Teacher rubric.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>MET | Vision brief separates quick walkthroughs from deeper coaching; observation, walkthrough, fidelity, calibration, coaching, and evidence tracker files define cadence.</t>
+          <t>MET | Formal ratings use the Matchbook SRR Teacher rubric; the Coach edition supports calibration and rehearsal; Get Better Faster supports action-step selection.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PARTIAL | 14/Observation_Record_Schema.md and Stakeholder_Permissions_Map.md connect evidence to data/visibility rules.</t>
+          <t>MET | 14/Observation_Record_Schema.md and Data_Dictionary.md store one formal Teacher-rubric practice rating per row and separate coaching guidance from scores.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>CLOSED | Tool cadence verified from vision brief plus walkthrough, fidelity, coaching, calibration, and evidence tracker files.</t>
+          <t>CLOSED 2026-06-15 | Folder 13 and Folder 06 crosswalks rebuilt around the ten Matchbook SRR Teacher-rubric practices.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>CLOSED 2026-06-04: Coaching tool cadence is specified through the folder vision brief and the observation, walkthrough, fidelity, calibration, coaching, and evidence tracker tools.</t>
+          <t>CLOSED 2026-06-15: Rubric governance corrected; R3xBP is protected framework IP, not the reporting rubric. Crosswalk, tools, tracker, and schema are aligned.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1895,17 +1895,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>68 ready · 1 MAJOR (rubric crosswalk)</t>
+          <t>68 ready - rubric crosswalk corrected</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>ALERT: Gated by the crosswalk rebuild against R³×BP Rubric v3. Station cards ready.</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>HIGH | Rebuild the rubric crosswalk | Re-align to R³×BP Rubric v3 (June 2026, 14 strands) — the system's one Major revision. Stale crosswalks in 13 &amp; 06.</t>
+          <t>OK: Rubric governance corrected - Teacher rubric is formal; Coach rubric and Get Better Faster guide coaching action steps.</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1952,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>MET | 14_DATA_TRACKING_AND_APP_READINESS/Observation_Record_Schema.md; 14_DATA_TRACKING_AND_APP_READINESS/Dashboard_Indicator_Map.md; 14_DATA_TRACKING_AND_APP_READINESS/Evidence_Conversion_Logic.md</t>
+          <t>MET | Observation_Record_Schema.md; Data_Dictionary.md; Dashboard_Indicator_Map.md | Formal reporting uses the ten Matchbook SRR Teacher-rubric practices and four mastery bands.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1977,12 +1972,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>CLOSED | Folder-to-data mapping is covered by module map, backend architecture, dictionary, object schemas, record schemas, and dashboard map.</t>
+          <t>CLOSED 2026-06-15 | Observation schema and dashboard indicators aligned to the Matchbook SRR Teacher rubric; coaching guidance fields are non-scoring.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>CLOSED 2026-06-04: Folder-to-data mapping verified through App_Module_Map.md, Backend_Data_Architecture.md, Data_Dictionary.md, Dashboard_Indicator_Map.md, object schemas, record schemas, and permissions map.</t>
+          <t>CLOSED 2026-06-15: Data Dictionary is unified and the formal observation model now separates Teacher-rubric ratings from Coach/GBF action-step guidance.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>OK: Now a buildable spec — Pulse schema gap closed.</t>
+          <t>OK: Formal observation model aligned to Teacher rubric; Coach/GBF guidance remains non-scoring.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -32348,7 +32343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -32363,7 +32358,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -32415,9 +32409,76 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rubric governance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Formal scoring source</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Matchbook SRR Teacher Rubric: ten reportable practices and four mastery bands.</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>Rubric governance</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Calibration companion</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Matchbook Coach Rubric supports calibration and rehearsal; it does not create a separate score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rubric governance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Action-step guidance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Get Better Faster supports coaching intervention selection; it is not a rating source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rubric governance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Protected framework IP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R3xBP is used to construct Matchbook materials; it is not the formal reporting rubric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>To update: edit, save (keep the name Matchbook_Culture_Data.xlsx), put it next to the HTML pages, refresh. Every view re-reads it on load.</t>
         </is>
